--- a/psychologist_forms/005_occupational_therapy_progress_note_template--psychologist_forms.xlsx
+++ b/psychologist_forms/005_occupational_therapy_progress_note_template--psychologist_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>treatmentplan</t>
+          <t>treatmentplan_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Treatment Plan</t>
+          <t>Treatmentplan 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>evaluation_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Evaluation 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>progressnotes</t>
+          <t>progressnotes_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Progress Notes</t>
+          <t>Progressnotes 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dischargeinfo</t>
+          <t>dischargeinfo_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Discharge Info</t>
+          <t>Dischargeinfo 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
